--- a/Analysis/exports/screener_2026-08-27.xlsx
+++ b/Analysis/exports/screener_2026-08-27.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 21:50</t>
+          <t>2026-08-27 22:42</t>
         </is>
       </c>
     </row>
